--- a/Raw_Data.xlsx
+++ b/Raw_Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\25244\Desktop\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D03FAD-E4E5-41D3-BD62-561D9F4DA57B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FF8EEA7-1AAD-45F6-A706-B554F1A229BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="447">
   <si>
     <t>Title</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -590,835 +590,1025 @@
     <t>Swe-bench: Can language models resolve real-world github issues?</t>
   </si>
   <si>
+    <t>Teaching Large Language Models to Self-Debug</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2304.05128</t>
+  </si>
+  <si>
+    <t>White-box Compiler FuzzingEmpowered by Large Language Models</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2310.15991</t>
+  </si>
+  <si>
+    <t>Is Self-Repair a Silver Bullet for Code Generation?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2306.09896</t>
+  </si>
+  <si>
+    <t>ChatDev: Communicative Agents for Software Development</t>
+  </si>
+  <si>
+    <t>Sarah Fakhoury, Markus Kuppe, Shuvendu K. Lahiri, Tahina Ramananandro, Nikhil Swamy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI-powered Code Review with LLMs: Early Results</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LaMDA: Language Models for Dialog Applications</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S21</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S22</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S23</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S26</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S27</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S28</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S29</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S33</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S34</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S35</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S36</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S37</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S38</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S39</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S41</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S42</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S43</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S44</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S45</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S46</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S47</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S48</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S49</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S51</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S52</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S53</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S54</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S55</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S56</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S57</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S58</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S59</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S60</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S61</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S62</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S63</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S64</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S65</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S66</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S67</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S68</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S69</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S70</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S71</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S72</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S73</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S74</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S75</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S76</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S77</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S78</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S79</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S80</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S81</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S82</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S83</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S84</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S85</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S86</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S87</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S88</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S89</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S90</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S91</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S92</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S93</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S94</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cheryl Lee, Chunqiu Steven Xia, Longji Yang, Jen-tse Huang, Zhouruixin Zhu, Lingming Zhang, Michael R. Lyu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lyuye Zhang, Kaixuan Li, Kairan Sun, Daoyuan Wu, Ye Liu, Haoye Tian, Yang Liu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yihao Qin, Shangwen Wang, Yiling Lou, Jinhao Dong, Kaixin Wang, Xiaoling Li, Xiaoguang Mao</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Minh Huynh Nguyen, Thang Phan Chau, Phong X. Nguyen, Nghi D. Q. Bui</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zeeshan Rasheed, Malik Abdul Sami, Muhammad Waseem, Kai-Kristian Kemell, Xiaofeng Wang, Anh Nguyen, Kari Systä, Pekka Abrahamsson</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bin Lei, Yuchen Li, Qiuwu Chen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yuntong Zhang, Haifeng Ruan, Zhiyu Fan, Abhik Roychoudhury</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Michele Tufano, Anisha Agarwal, Jinu Jang, Roshanak Zilouchian Moghaddam, Neel Sundaresan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chenyuan Yang, Xuheng Li, Md Rakib Hossain Misu, Jianan Yao, Weidong Cui, Yeyun Gong, Chris Hawblitzel, Shuvendu Lahiri, Jacob R. Lorch, Shuai Lu, Fan Yang, Ziqiao Zhou, Shan Lu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sanjiban Choudhury, Paloma Sodhi</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Xunzhu Tang, Kisub Kim, Yewei Song, Cedric Lothritz, Bei Li, Saad Ezzini, Haoye Tian, Jacques Klein, Tegawende F. Bissyande</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kechi Zhang, Jia Li, Ge Li, Xianjie Shi, Zhi Jin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zeeshan Rasheed, Malik Abdul Sami, Kai-Kristian Kemell, Muhammad Waseem, Mika Saari, Kari Systä, Pekka Abrahamsson</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dong Chen, Shaoxin Lin, Muhan Zeng, Daoguang Zan, Jian-Gang Wang, Anton Cheshkov, Jun Sun, Hao Yu, Guoliang Dong, Artem Aliev, Jie Wang, Xiao Cheng, Guangtai Liang, Yuchi Ma, Pan Bian, Tao Xie, Qianxiang Wang</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Daoguang Zan, Ailun Yu, Wei Liu, Dong Chen, Bo Shen, Wei Li, Yafen Yao, Yongshun Gong, Xiaolin Chen, Bei Guan, Zhiguang Yang, Yongji Wang, Qianxiang Wang, Lizhen Cui</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wei Ma, Daoyuan Wu, Yuqiang Sun, Tianwen Wang, Shangqing Liu, Jian Zhang, Yue Xue, Yang Liu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kexun Zhang, Weiran Yao, Zuxin Liu, Yihao Feng, Zhiwei Liu, Rithesh Murthy, Tian Lan, Lei Li, Renze Lou, Jiacheng Xu, Bo Pang, Yingbo Zhou, Shelby Heinecke, Silvio Savarese, Huan Wang, Caiming Xiong</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mohammadmehdi Ataei, Hyunmin Cheong, Daniele Grandi, Ye Wang, Nigel Morris, Alexander Tessier</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Md Nakhla Rafi, Dong Jae Kim, Tse-Hsun Chen, Shaowei Wang</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Simiao Zhang, Jiaping Wang, Guoliang Dong, Jun Sun, Yueling Zhang, Geguang Pu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Malik Abdul Sami, Muhammad Waseem, Zeeshan Rasheed, Mika Saari, Kari Systä, Pekka Abrahamsson</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Arsham Gholamzadeh Khoee, Yinan Yu, Robert Feldt, Andris Freimanis, Patrick Andersson Rhodin, Dhasarathy Parthasarathy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yingwei Ma, Qingping Yang, Rongyu Cao, Binhua Li, Fei Huang, Yongbin Li</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chen Qian, Jiahao Li, Yufan Dang, Wei Liu, YiFei Wang, Zihao Xie, Weize Chen, Cheng Yang, Yingli Zhang, Zhiyuan Liu, Maosong Sun</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Richard Fang, Rohan Bindu, Akul Gupta, Daniel Kang</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zhiyuan Wei, Jing Sun, Zijiang Zhang, Xianhao Zhang</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mohamad Fakih, Rahul Dharmaji, Yasamin Moghaddas, Gustavo Quiros Araya, Oluwatosin Ogundare, Mohammad Abdullah Al Faruque</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wei Tao, Yucheng Zhou, Yanlin Wang, Wenqiang Zhang, Hongyu Zhang, Yu Cheng</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Md. Ashraful Islam, Mohammed Eunus Ali, Md Rizwan Parvez</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dongming Jin, Zhi Jin, Xiaohong Chen, Chunhui Wang</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yizhou Liu, Pengfei Gao, Xinchen Wang, Jie Liu, Yexuan Shi, Zhao Zhang, Chao Peng</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Daman Arora, Atharv Sonwane, Nalin Wadhwa, Abhav Mehrotra, Saiteja Utpala, Ramakrishna Bairi, Aditya Kanade, Nagarajan Natarajan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Junyou Li, Qin Zhang, Yangbin Yu, Qiang Fu, Deheng Ye</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zhuoyun Du, Chen Qian, Wei Liu, Zihao Xie, Yifei Wang, Yufan Dang, Weize Chen, Cheng Yang</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zhenyu Mao, Jialong Li, Dongming Jin, Munan Li, Kenji Tei</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Haolin Jin, Zechao Sun, Huaming Chen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chen Qian, Zihao Xie, Yifei Wang, Wei Liu, Yufan Dang, Zhuoyun Du, Weize Chen, Cheng Yang, Zhiyuan Liu, Maosong Sun</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yoichi Ishibashi, Yoshimasa Nishimura</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Haifeng Ruan, Yuntong Zhang, Abhik Roychoudhury</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>John Yang, Carlos E. Jimenez, Alexander Wettig, Kilian Lieret, Shunyu Yao, Karthik Narasimhan, Ofir Press</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Noble Saji Mathews, Meiyappan Nagappan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Feng Lin, Dong Jae Kim, Tse-Husn (Peter)Chen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zhitao Wang, Wei Wang, Zirao Li, Long Wang, Can Yi, Xinjie Xu, Luyang Cao, Hanjing Su, Shouzhi Chen, Jun Zhou</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dawen Zhang, Xiwei Xu, Chen Wang, Zhenchang Xing, Robert Mao</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sai Zhang, Zhenchang Xing, Ronghui Guo, Fangzhou Xu, Lei Chen, Zhaoyuan Zhang, Xiaowang Zhang, Zhiyong Feng, Zhiqiang Zhuang</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Juyeon Yoon; Robert Feldt; Shin Yoo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zhe Liu, Cheng Li, Chunyang Chen, Junjie Wang, Boyu Wu, Yawen Wang, Jun Hu, Qing Wang</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jiahong Xiang, Xiaoyang Xu, Fanchu Kong, Mingyuan Wu, Zizheng Zhang, Haotian Zhang, Yuqun Zhang</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zixiao Zhao, Jing Sun, Zhiyuan Wei, Cheng-Hao Cai, Zhe Hou, Jin Song Dong</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ahmed R. Sadik, Sebastian Brulin, Markus Olhofer, Antonello Ceravola, Frank Joublin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yue Hu, Yuzhu Cai, Yaxin Du, Xinyu Zhu, Xiangrui Liu, Zijie Yu, Yuchen Hou, Shuo Tang, Siheng Chen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zihan Liu, Ruinan Zeng, Dongxia Wang, Gengyun Peng, Jingyi Wang, Qiang Liu, Peiyu Liu, Wenhai Wang</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Xuanming Zhang, Yuxuan Chen, Yuan Yuan, Minlie Huang</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zhiqiang Yuan, Weitong Chen, Hanlin Wang, Kai Yu, Xin Peng, Yiling Lou</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Leilei Lin, Yingming Zhou, Wenlong Chen, Chen Qian</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Huan Zhang, Wei Cheng, Yuhan Wu, Wei Hu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weiqing Yang, Hanbin Wang, Zhenghao Liu, Xinze Li, Yukun Yan, Shuo Wang, Yu Gu, Minghe Yu, Zhiyuan Liu, Ge Yu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Forough Mehralian, Titus Barik, Jeff Nichols, Amanda Swearngin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dong Huang, Jie M.Zhang, Michael Luck, Qingwen Bu, Yuhao Qing, Heming Cui</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weize Chen, Yusheng Su, Jingwei Zuo, Cheng Yang, Chenfei Yuan, Chi-Min Chan, Heyang Yu, Yaxi Lu, Yi-Hsin Hung, Chen Qian, Yujia Qin, Xin Cong, Ruobing Xie, Zhiyuan Liu, Maosong Sun, Jie Zhou</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Guangyao Chen, Siwei Dong, Yu Shu, Ge Zhang, Jaward Sesay, Börje F. Karlsson, Jie Fu, Yemin Shi</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Qingyun Wu, Gagan Bansal, Jieyu Zhang, Yiran Wu, Beibin Li, Erkang Zhu, Li Jiang, Xiaoyun Zhang, Shaokun Zhang, Jiale Liu, Ahmed Hassan Awadallah, Ryen W White, Doug Burger, Chi Wang</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zeeshan Rasheed, Muhammad Waseem, Kai-Kristian Kemell, Wang Xiaofeng, Anh Nguyen Duc, Kari Systä, Pekka Abrahamsson</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Maryam Taeb, Amanda Swearngin, Eldon Schoop, Ruijia Cheng, Yue Jiang, Jeffrey Nichols</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Guohao Li, Hasan Abed Al Kader Hammoud, Hani Itani, Dmitrii Khizbullin, Bernard Ghanem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Guang Yang, Yu Zhou, Xiang Chen, Xiangyu Zhang, Terry Yue Zhuo, Taolue Chen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Seungjun Moon, Hyungjoo Chae, Yongho Song, Taeyoon Kwon, Dongjin Kang, Kai Tzu-iunn Ong, Seung-won Hwang, Jinyoung Yeo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chen Qian, Wei Liu, Hongzhang Liu, Nuo Chen, Yufan Dang, Jiahao Li, Cheng Yang, Weize Chen, Yusheng Su, Xin Cong, Juyuan Xu, Dahai Li, Zhiyuan Liu, Maosong Sun</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nalin Wadhwa, Jui Pradhan, Atharv Sonwane, Surya Prakash Sahu, Nagarajan Natarajan, Aditya Kanade, Suresh Parthasarathy, Sriram Rajamani</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zijun Liu, Yanzhe Zhang, Peng Li, Yang Liu, Diyi Yang</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yu Hao, Weiteng Chen, Ziqiao Zhou, Weidong Cui</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chen Qian, Yufan Dang, Jiahao Li, Wei Liu, Zihao Xie, Yifei Wang, Weize Chen, Cheng Yang, Xin Cong, Xiaoyin Che, Zhiyuan Liu, Maosong Sun</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Martin Josifoski, Lars Klein, Maxime Peyrard, Nicolas Baldwin, Yifei Li, Saibo Geng, Julian Paul Schnitzler, Yuxing Yao, Jiheng Wei, Debjit Paul, Robert West</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chunqiu Steven Xia, Matteo Paltenghi, Jia Le Tian, Michael Pradel, Lingming Zhang</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Binfeng Xu, Xukun Liu, Hua Shen, Zeyu Han, Yuhan Li, Murong Yue, Zhiyuan Peng, Yuchen Liu, Ziyu Yao, Dongkuan Xu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zhou Yang, Zhipeng Zhao, Chenyu Wang, Jieke Shi, Dongsum Kim, Donggyun Han, David Lo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hanbin Wang, Zhenghao Liu, Shuo Wang, Ganqu Cui, Ning Ding, Zhiyuan Liu, Ge Yu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yiheng Xu, Hongjin Su, Chen Xing, Boyu Mi, Qian Liu, Weijia Shi, Binyuan Hui, Fan Zhou, Yitao Liu, Tianbao Xie, Zhoujun Cheng, Siheng Zhao, Lingpeng Kong, Bailin Wang, Caiming Xiong, Tao Yu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zhe Liu, Chunyang Chen, Junjie Wang, Mengzhuo Chen, Boyu Wu, Xing Che, Dandan Wang, Qing Wang</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sirui Hong, Mingchen Zhuge, Jonathan Chen, Xiawu Zheng, Yuheng Cheng, Ceyao Zhang, Jinlin Wang, Zili Wang, Steven Ka Shing Yau, Zijuan Lin, Liyang Zhou, Chenyu Ran, Lingfeng Xiao, Chenglin Wu, Jürgen Schmidhuber</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yashar Talebirad, Amirhossein Nadiri</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Eric Zelikman, Qian Huang, Gabriel Poesia, Noah D. Goodman, Nick Haber</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zhenchang Xing, Qing Huang, Yu Cheng, Liming Zhu, Qinghua Lu, Xiwei Xu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Zefan Wang, Zichuan Liu, Yingying Zhang, Aoxiao Zhong, Jihong Wang, Fengbin Yin, Lunting Fan, Lingfei Wu, Qingsong Wen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yihong Dong, Xue Jiang, Zhi Jin, Ge Li</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kechi Zhang, Zhuo Li, Jia Li, Ge Li, Zhi Jin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gang Fan, Xiaoheng Xie, Xunjin Zheng, Yinan Liang, Peng Di</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Carlos E. Jimenez, John Yang, Alexander Wettig, Shunyu Yao, Kexin Pei, Ofir Press, Karthik Narasimhan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Xinyun Chen, Maxwell Lin, Nathanael Schärli, Denny Zhou</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chenyuan Yang, Yinlin Deng, Runyu Lu, Jiayi Yao, Jiawei Liu, Reyhaneh Jabbarvand, Lingming Zhang</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Theo X. Olausson, Jeevana Priya Inala, Chenglong Wang, Jianfeng Gao, Armando Solar-Lezama</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Romal Thoppilan, Daniel De Freitas, Jamie Hall, Noam Shazeer, Apoorv Kulshreshtha, Heng-Tze Cheng, Alicia Jin, Taylor Bos, Leslie Baker, Yu Du, YaGuang Li, Hongrae Lee, Huaixiu Steven Zheng, Amin Ghafouri, Marcelo Menegali, Yanping Huang, Maxim Krikun, Dmitry Lepikhin, James Qin, Dehao Chen, Yuanzhong Xu, Zhifeng Chen, Adam Roberts, Maarten Bosma, Vincent Zhao, Yanqi Zhou, Chung-Ching Chang, Igor Krivokon, Will Rusch, Marc Pickett, Pranesh Srinivasan, Laichee Man, Kathleen Meier-Hellstern, Meredith Ringel Morris, Tulsee Doshi, Renelito Delos Santos, Toju Duke, Johnny Soraker, Ben Zevenbergen, Vinodkumar Prabhakaran, Mark Diaz, Ben Hutchinson, Kristen Olson, Alejandra Molina, Erin Hoffman-John, Josh Lee, Lora Aroyo, Ravi Rajakumar, Alena Butryna, Matthew Lamm, Viktoriya Kuzmina, Joe Fenton, Aaron Cohen, Rachel Bernstein, Ray Kurzweil, Blaise Aguera-Arcas, Claire Cui, Marian Croak, Ed Chi, Quoc Le</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2404.17153</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ACFIX: Guiding LLMs with Mined Common  RBAC Practices for Context-Aware Repair of  Access Control Vulnerabilities in Smart Contracts </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">FixAgent: Hierarchical Multi-Agent Framework for Unified Software  Debugging </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GoNoGo: An Efficient LLM-based Multi-Agent System for Streamlining Automotive Software Release Decision-Making</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SOEN-101: Code Generation by Emulating  Software Process Models Using Large Language  Model Agents</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Seeing is Believing: Vision-driven Automated Mobile GUI Testing via Multimodal Large Language Model</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A Pair Programming Framework for Code Generation via Multi-Plan Exploration and Feedback-Driven Refinement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>COAST: Enhancing the Code Debugging Ability of LLMs via Communicative Agent Based Data Refinement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A Dynamic LLM-Agent Network: An LLM-agent Collaboration Framework with Agent Team Optimization</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gentopia.AI: A Collaborative Platform for Tool-Augmented LLMs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MetaGPT: Meta Programming for A Multi-Agent Collaborative Framework</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Parsel: Algorithmic Reasoning with Language Models by Composing Decompositions</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S95</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S96</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S97</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S98</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S104</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S105</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S106</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Huy Nhat Phan, Tien N. Nguyen, Phong X. Nguyen, Nghi D. Q. Bui</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HyperAgent: Generalist Software Engineering Agents to Solve Coding Tasks at Scale</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2409.16299</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INDICT: code generation with internal dialogues of critiques for both security and helpfulness</t>
+  </si>
+  <si>
+    <t>https://proceedings.neurips.cc/paper_files/paper/2024/file/9b812ee4b831c21e14156ced8659197c-Paper-Conference.pdf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hung Le, Yingbo Zhou, Caiming Xiong, Silvio Savarese, Doyen Sahoo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SOEN-101: Code Generation by Emulating Software Process Models Using Large Language Model Agents</t>
+  </si>
+  <si>
+    <t>ICSE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Feng Lin, Dong Jae Kim, Tse-Hsun Chen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/10.1109/ICSE55347.2025.00140</t>
+  </si>
+  <si>
+    <t>Noah Shinn, Federico Cassano, Ashwin Gopinath, Karthik Narasimhan, Shunyu Yao</t>
+  </si>
+  <si>
+    <t>Reflexion: Language agents with verbal reinforcement learning</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/10.5555/3666122.3666499</t>
+  </si>
+  <si>
+    <t>Xiangyan Liu, Bo Lan, Zhiyuan Hu, Yang Liu, Zhicheng Zhang, Fei Wang, Michael Shieh, Wenmeng Zhou</t>
+  </si>
+  <si>
+    <t>CodexGraph: Bridging Large Language Models and Code Repositories via Code Graph Databases</t>
+  </si>
+  <si>
+    <t>https://aclanthology.org/2025.naacl-long.7.pdf</t>
+  </si>
+  <si>
+    <t>ACL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gelei Deng, Yi Liu, Víctor Mayoral-Vilches, Peng Liu, Yuekang Li, Yuan Xu, Tianwei Zhang, Yang Liu, Martin Pinzger, Stefan Rass</t>
+  </si>
+  <si>
+    <t>PENTESTGPT: evaluating and harnessing large language models for automated penetration testing</t>
+  </si>
+  <si>
+    <t>SEC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/10.5555/3698900.3698948</t>
+  </si>
+  <si>
+    <t>Malik Abdul Sami, Muhammad Waseem, Zheying Zhang, Zeeshan Rasheed, Kari Systä, Pekka Abrahamsson</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI based Multiagent Approach for Requirements Elicitation and Analysis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jierui Li, Hung Le, Yingbo Zhou, Caiming Xiong, Silvio Savarese, Doyen Sahoo</t>
+  </si>
+  <si>
+    <t>CodeTree: Agent-guided Tree Search for Code Generation with Large Language Models</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2201.08239</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2411.04329</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>https://arxiv.org/abs/2310.06770</t>
-  </si>
-  <si>
-    <t>Teaching Large Language Models to Self-Debug</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2304.05128</t>
-  </si>
-  <si>
-    <t>White-box Compiler FuzzingEmpowered by Large Language Models</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2310.15991</t>
-  </si>
-  <si>
-    <t>Is Self-Repair a Silver Bullet for Code Generation?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2306.09896</t>
-  </si>
-  <si>
-    <t>ChatDev: Communicative Agents for Software Development</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2201.08239</t>
-  </si>
-  <si>
-    <t>Sarah Fakhoury, Markus Kuppe, Shuvendu K. Lahiri, Tahina Ramananandro, Nikhil Swamy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AI-powered Code Review with LLMs: Early Results</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LaMDA: Language Models for Dialog Applications</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S11</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S12</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S13</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S14</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S15</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S16</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S17</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S18</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S19</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S21</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S22</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S23</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S24</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S26</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S27</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S28</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S29</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S31</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S32</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S33</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S34</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S35</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S36</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S37</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S38</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S39</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S40</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S41</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S42</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S43</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S44</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S45</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S46</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S47</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S48</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S49</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S50</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S51</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S52</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S53</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S54</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S55</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S56</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S57</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S58</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S59</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S60</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S61</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S62</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S63</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S64</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S65</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S66</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S67</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S68</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S69</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S70</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S71</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S72</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S73</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S74</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S75</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S76</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S77</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S78</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S79</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S80</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S81</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S82</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S83</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S84</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S85</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S86</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S87</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S88</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S89</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S90</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S91</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S92</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S93</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S94</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cheryl Lee, Chunqiu Steven Xia, Longji Yang, Jen-tse Huang, Zhouruixin Zhu, Lingming Zhang, Michael R. Lyu</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Lyuye Zhang, Kaixuan Li, Kairan Sun, Daoyuan Wu, Ye Liu, Haoye Tian, Yang Liu</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Yihao Qin, Shangwen Wang, Yiling Lou, Jinhao Dong, Kaixin Wang, Xiaoling Li, Xiaoguang Mao</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Minh Huynh Nguyen, Thang Phan Chau, Phong X. Nguyen, Nghi D. Q. Bui</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Zeeshan Rasheed, Malik Abdul Sami, Muhammad Waseem, Kai-Kristian Kemell, Xiaofeng Wang, Anh Nguyen, Kari Systä, Pekka Abrahamsson</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bin Lei, Yuchen Li, Qiuwu Chen</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Yuntong Zhang, Haifeng Ruan, Zhiyu Fan, Abhik Roychoudhury</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Michele Tufano, Anisha Agarwal, Jinu Jang, Roshanak Zilouchian Moghaddam, Neel Sundaresan</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Chenyuan Yang, Xuheng Li, Md Rakib Hossain Misu, Jianan Yao, Weidong Cui, Yeyun Gong, Chris Hawblitzel, Shuvendu Lahiri, Jacob R. Lorch, Shuai Lu, Fan Yang, Ziqiao Zhou, Shan Lu</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sanjiban Choudhury, Paloma Sodhi</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Xunzhu Tang, Kisub Kim, Yewei Song, Cedric Lothritz, Bei Li, Saad Ezzini, Haoye Tian, Jacques Klein, Tegawende F. Bissyande</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Kechi Zhang, Jia Li, Ge Li, Xianjie Shi, Zhi Jin</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Zeeshan Rasheed, Malik Abdul Sami, Kai-Kristian Kemell, Muhammad Waseem, Mika Saari, Kari Systä, Pekka Abrahamsson</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dong Chen, Shaoxin Lin, Muhan Zeng, Daoguang Zan, Jian-Gang Wang, Anton Cheshkov, Jun Sun, Hao Yu, Guoliang Dong, Artem Aliev, Jie Wang, Xiao Cheng, Guangtai Liang, Yuchi Ma, Pan Bian, Tao Xie, Qianxiang Wang</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Daoguang Zan, Ailun Yu, Wei Liu, Dong Chen, Bo Shen, Wei Li, Yafen Yao, Yongshun Gong, Xiaolin Chen, Bei Guan, Zhiguang Yang, Yongji Wang, Qianxiang Wang, Lizhen Cui</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wei Ma, Daoyuan Wu, Yuqiang Sun, Tianwen Wang, Shangqing Liu, Jian Zhang, Yue Xue, Yang Liu</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Kexun Zhang, Weiran Yao, Zuxin Liu, Yihao Feng, Zhiwei Liu, Rithesh Murthy, Tian Lan, Lei Li, Renze Lou, Jiacheng Xu, Bo Pang, Yingbo Zhou, Shelby Heinecke, Silvio Savarese, Huan Wang, Caiming Xiong</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mohammadmehdi Ataei, Hyunmin Cheong, Daniele Grandi, Ye Wang, Nigel Morris, Alexander Tessier</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Md Nakhla Rafi, Dong Jae Kim, Tse-Hsun Chen, Shaowei Wang</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Simiao Zhang, Jiaping Wang, Guoliang Dong, Jun Sun, Yueling Zhang, Geguang Pu</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Malik Abdul Sami, Muhammad Waseem, Zeeshan Rasheed, Mika Saari, Kari Systä, Pekka Abrahamsson</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Arsham Gholamzadeh Khoee, Yinan Yu, Robert Feldt, Andris Freimanis, Patrick Andersson Rhodin, Dhasarathy Parthasarathy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Yingwei Ma, Qingping Yang, Rongyu Cao, Binhua Li, Fei Huang, Yongbin Li</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Chen Qian, Jiahao Li, Yufan Dang, Wei Liu, YiFei Wang, Zihao Xie, Weize Chen, Cheng Yang, Yingli Zhang, Zhiyuan Liu, Maosong Sun</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Richard Fang, Rohan Bindu, Akul Gupta, Daniel Kang</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Zhiyuan Wei, Jing Sun, Zijiang Zhang, Xianhao Zhang</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mohamad Fakih, Rahul Dharmaji, Yasamin Moghaddas, Gustavo Quiros Araya, Oluwatosin Ogundare, Mohammad Abdullah Al Faruque</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wei Tao, Yucheng Zhou, Yanlin Wang, Wenqiang Zhang, Hongyu Zhang, Yu Cheng</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Md. Ashraful Islam, Mohammed Eunus Ali, Md Rizwan Parvez</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dongming Jin, Zhi Jin, Xiaohong Chen, Chunhui Wang</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Yizhou Liu, Pengfei Gao, Xinchen Wang, Jie Liu, Yexuan Shi, Zhao Zhang, Chao Peng</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Daman Arora, Atharv Sonwane, Nalin Wadhwa, Abhav Mehrotra, Saiteja Utpala, Ramakrishna Bairi, Aditya Kanade, Nagarajan Natarajan</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Junyou Li, Qin Zhang, Yangbin Yu, Qiang Fu, Deheng Ye</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Zhuoyun Du, Chen Qian, Wei Liu, Zihao Xie, Yifei Wang, Yufan Dang, Weize Chen, Cheng Yang</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Zhenyu Mao, Jialong Li, Dongming Jin, Munan Li, Kenji Tei</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Haolin Jin, Zechao Sun, Huaming Chen</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Chen Qian, Zihao Xie, Yifei Wang, Wei Liu, Yufan Dang, Zhuoyun Du, Weize Chen, Cheng Yang, Zhiyuan Liu, Maosong Sun</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Yoichi Ishibashi, Yoshimasa Nishimura</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Haifeng Ruan, Yuntong Zhang, Abhik Roychoudhury</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>John Yang, Carlos E. Jimenez, Alexander Wettig, Kilian Lieret, Shunyu Yao, Karthik Narasimhan, Ofir Press</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Noble Saji Mathews, Meiyappan Nagappan</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Feng Lin, Dong Jae Kim, Tse-Husn (Peter)Chen</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Zhitao Wang, Wei Wang, Zirao Li, Long Wang, Can Yi, Xinjie Xu, Luyang Cao, Hanjing Su, Shouzhi Chen, Jun Zhou</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dawen Zhang, Xiwei Xu, Chen Wang, Zhenchang Xing, Robert Mao</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sai Zhang, Zhenchang Xing, Ronghui Guo, Fangzhou Xu, Lei Chen, Zhaoyuan Zhang, Xiaowang Zhang, Zhiyong Feng, Zhiqiang Zhuang</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Juyeon Yoon; Robert Feldt; Shin Yoo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Zhe Liu, Cheng Li, Chunyang Chen, Junjie Wang, Boyu Wu, Yawen Wang, Jun Hu, Qing Wang</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Jiahong Xiang, Xiaoyang Xu, Fanchu Kong, Mingyuan Wu, Zizheng Zhang, Haotian Zhang, Yuqun Zhang</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Zixiao Zhao, Jing Sun, Zhiyuan Wei, Cheng-Hao Cai, Zhe Hou, Jin Song Dong</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ahmed R. Sadik, Sebastian Brulin, Markus Olhofer, Antonello Ceravola, Frank Joublin</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Yue Hu, Yuzhu Cai, Yaxin Du, Xinyu Zhu, Xiangrui Liu, Zijie Yu, Yuchen Hou, Shuo Tang, Siheng Chen</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Zihan Liu, Ruinan Zeng, Dongxia Wang, Gengyun Peng, Jingyi Wang, Qiang Liu, Peiyu Liu, Wenhai Wang</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Xuanming Zhang, Yuxuan Chen, Yuan Yuan, Minlie Huang</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Zhiqiang Yuan, Weitong Chen, Hanlin Wang, Kai Yu, Xin Peng, Yiling Lou</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Leilei Lin, Yingming Zhou, Wenlong Chen, Chen Qian</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Huan Zhang, Wei Cheng, Yuhan Wu, Wei Hu</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Weiqing Yang, Hanbin Wang, Zhenghao Liu, Xinze Li, Yukun Yan, Shuo Wang, Yu Gu, Minghe Yu, Zhiyuan Liu, Ge Yu</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Forough Mehralian, Titus Barik, Jeff Nichols, Amanda Swearngin</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dong Huang, Jie M.Zhang, Michael Luck, Qingwen Bu, Yuhao Qing, Heming Cui</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Weize Chen, Yusheng Su, Jingwei Zuo, Cheng Yang, Chenfei Yuan, Chi-Min Chan, Heyang Yu, Yaxi Lu, Yi-Hsin Hung, Chen Qian, Yujia Qin, Xin Cong, Ruobing Xie, Zhiyuan Liu, Maosong Sun, Jie Zhou</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Guangyao Chen, Siwei Dong, Yu Shu, Ge Zhang, Jaward Sesay, Börje F. Karlsson, Jie Fu, Yemin Shi</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Qingyun Wu, Gagan Bansal, Jieyu Zhang, Yiran Wu, Beibin Li, Erkang Zhu, Li Jiang, Xiaoyun Zhang, Shaokun Zhang, Jiale Liu, Ahmed Hassan Awadallah, Ryen W White, Doug Burger, Chi Wang</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Zeeshan Rasheed, Muhammad Waseem, Kai-Kristian Kemell, Wang Xiaofeng, Anh Nguyen Duc, Kari Systä, Pekka Abrahamsson</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Maryam Taeb, Amanda Swearngin, Eldon Schoop, Ruijia Cheng, Yue Jiang, Jeffrey Nichols</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Guohao Li, Hasan Abed Al Kader Hammoud, Hani Itani, Dmitrii Khizbullin, Bernard Ghanem</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Guang Yang, Yu Zhou, Xiang Chen, Xiangyu Zhang, Terry Yue Zhuo, Taolue Chen</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Seungjun Moon, Hyungjoo Chae, Yongho Song, Taeyoon Kwon, Dongjin Kang, Kai Tzu-iunn Ong, Seung-won Hwang, Jinyoung Yeo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Chen Qian, Wei Liu, Hongzhang Liu, Nuo Chen, Yufan Dang, Jiahao Li, Cheng Yang, Weize Chen, Yusheng Su, Xin Cong, Juyuan Xu, Dahai Li, Zhiyuan Liu, Maosong Sun</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Nalin Wadhwa, Jui Pradhan, Atharv Sonwane, Surya Prakash Sahu, Nagarajan Natarajan, Aditya Kanade, Suresh Parthasarathy, Sriram Rajamani</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Zijun Liu, Yanzhe Zhang, Peng Li, Yang Liu, Diyi Yang</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Yu Hao, Weiteng Chen, Ziqiao Zhou, Weidong Cui</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Chen Qian, Yufan Dang, Jiahao Li, Wei Liu, Zihao Xie, Yifei Wang, Weize Chen, Cheng Yang, Xin Cong, Xiaoyin Che, Zhiyuan Liu, Maosong Sun</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Martin Josifoski, Lars Klein, Maxime Peyrard, Nicolas Baldwin, Yifei Li, Saibo Geng, Julian Paul Schnitzler, Yuxing Yao, Jiheng Wei, Debjit Paul, Robert West</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Chunqiu Steven Xia, Matteo Paltenghi, Jia Le Tian, Michael Pradel, Lingming Zhang</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Binfeng Xu, Xukun Liu, Hua Shen, Zeyu Han, Yuhan Li, Murong Yue, Zhiyuan Peng, Yuchen Liu, Ziyu Yao, Dongkuan Xu</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Zhou Yang, Zhipeng Zhao, Chenyu Wang, Jieke Shi, Dongsum Kim, Donggyun Han, David Lo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hanbin Wang, Zhenghao Liu, Shuo Wang, Ganqu Cui, Ning Ding, Zhiyuan Liu, Ge Yu</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Yiheng Xu, Hongjin Su, Chen Xing, Boyu Mi, Qian Liu, Weijia Shi, Binyuan Hui, Fan Zhou, Yitao Liu, Tianbao Xie, Zhoujun Cheng, Siheng Zhao, Lingpeng Kong, Bailin Wang, Caiming Xiong, Tao Yu</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Zhe Liu, Chunyang Chen, Junjie Wang, Mengzhuo Chen, Boyu Wu, Xing Che, Dandan Wang, Qing Wang</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sirui Hong, Mingchen Zhuge, Jonathan Chen, Xiawu Zheng, Yuheng Cheng, Ceyao Zhang, Jinlin Wang, Zili Wang, Steven Ka Shing Yau, Zijuan Lin, Liyang Zhou, Chenyu Ran, Lingfeng Xiao, Chenglin Wu, Jürgen Schmidhuber</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Yashar Talebirad, Amirhossein Nadiri</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Eric Zelikman, Qian Huang, Gabriel Poesia, Noah D. Goodman, Nick Haber</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Zhenchang Xing, Qing Huang, Yu Cheng, Liming Zhu, Qinghua Lu, Xiwei Xu</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Zefan Wang, Zichuan Liu, Yingying Zhang, Aoxiao Zhong, Jihong Wang, Fengbin Yin, Lunting Fan, Lingfei Wu, Qingsong Wen</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Yihong Dong, Xue Jiang, Zhi Jin, Ge Li</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Kechi Zhang, Zhuo Li, Jia Li, Ge Li, Zhi Jin</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gang Fan, Xiaoheng Xie, Xunjin Zheng, Yinan Liang, Peng Di</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Carlos E. Jimenez, John Yang, Alexander Wettig, Shunyu Yao, Kexin Pei, Ofir Press, Karthik Narasimhan</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Xinyun Chen, Maxwell Lin, Nathanael Schärli, Denny Zhou</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Chenyuan Yang, Yinlin Deng, Runyu Lu, Jiayi Yao, Jiawei Liu, Reyhaneh Jabbarvand, Lingming Zhang</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Theo X. Olausson, Jeevana Priya Inala, Chenglong Wang, Jianfeng Gao, Armando Solar-Lezama</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Romal Thoppilan, Daniel De Freitas, Jamie Hall, Noam Shazeer, Apoorv Kulshreshtha, Heng-Tze Cheng, Alicia Jin, Taylor Bos, Leslie Baker, Yu Du, YaGuang Li, Hongrae Lee, Huaixiu Steven Zheng, Amin Ghafouri, Marcelo Menegali, Yanping Huang, Maxim Krikun, Dmitry Lepikhin, James Qin, Dehao Chen, Yuanzhong Xu, Zhifeng Chen, Adam Roberts, Maarten Bosma, Vincent Zhao, Yanqi Zhou, Chung-Ching Chang, Igor Krivokon, Will Rusch, Marc Pickett, Pranesh Srinivasan, Laichee Man, Kathleen Meier-Hellstern, Meredith Ringel Morris, Tulsee Doshi, Renelito Delos Santos, Toju Duke, Johnny Soraker, Ben Zevenbergen, Vinodkumar Prabhakaran, Mark Diaz, Ben Hutchinson, Kristen Olson, Alejandra Molina, Erin Hoffman-John, Josh Lee, Lora Aroyo, Ravi Rajakumar, Alena Butryna, Matthew Lamm, Viktoriya Kuzmina, Joe Fenton, Aaron Cohen, Rachel Bernstein, Ray Kurzweil, Blaise Aguera-Arcas, Claire Cui, Marian Croak, Ed Chi, Quoc Le</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2404.17153</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">ACFIX: Guiding LLMs with Mined Common  RBAC Practices for Context-Aware Repair of  Access Control Vulnerabilities in Smart Contracts </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">FixAgent: Hierarchical Multi-Agent Framework for Unified Software  Debugging </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GoNoGo: An Efficient LLM-based Multi-Agent System for Streamlining Automotive Software Release Decision-Making</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SOEN-101: Code Generation by Emulating  Software Process Models Using Large Language  Model Agents</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Seeing is Believing: Vision-driven Automated Mobile GUI Testing via Multimodal Large Language Model</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A Pair Programming Framework for Code Generation via Multi-Plan Exploration and Feedback-Driven Refinement</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>COAST: Enhancing the Code Debugging Ability of LLMs via Communicative Agent Based Data Refinement</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A Dynamic LLM-Agent Network: An LLM-agent Collaboration Framework with Agent Team Optimization</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gentopia.AI: A Collaborative Platform for Tool-Augmented LLMs</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MetaGPT: Meta Programming for A Multi-Agent Collaborative Framework</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Parsel: Algorithmic Reasoning with Language Models by Composing Decompositions</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2409.00038</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sihao Hu, Tiansheng Huang, Fatih İlhan, Selim Furkan Tekin, Ling Liu</t>
+  </si>
+  <si>
+    <t>Large Language Model-Powered Smart Contract Vulnerability Detection: New Perspectives</t>
+  </si>
+  <si>
+    <t>TPS-ISA</t>
+  </si>
+  <si>
+    <t>https://www.computer.org/csdl/proceedings-article/tps-isa/2023/238500a297/1UAj658V0c0</t>
+  </si>
+  <si>
+    <t>Bin Lei, Yuchen Li, Yiming Zeng, Tao Ren, Yi Luo, Tianyu Shi, Zitian Gao, Zeyu Hu, Weitai Kang, Qiuwu Chen</t>
+  </si>
+  <si>
+    <t>Infant Agent: A Tool-Integrated, Logic-Driven Agent with Cost-Effective API Usage</t>
+  </si>
+  <si>
+    <t>arXiv</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2411.01114</t>
+  </si>
+  <si>
+    <t>Samuel Holt, Max Ruiz Luyten, Mihaela van der Schaar</t>
+  </si>
+  <si>
+    <t>{L2mac: Large language model automatic computer for unbounded code generation</t>
+  </si>
+  <si>
+    <t>ICLR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://openreview.net/forum?id=EhrzQwsV4K</t>
+  </si>
+  <si>
+    <t>Qian Wang, Tianyu Wang, Zhenheng Tang, Qinbin Li, Nuo Chen, Jingsheng Liang, Bingsheng He</t>
+  </si>
+  <si>
+    <t>MegaAgent: A Practical Framework for Autonomous Cooperation in Large-Scale LLM Agent Systems</t>
+  </si>
+  <si>
+    <t>https://aclanthology.org/2025.findings-acl.259/</t>
   </si>
 </sst>
 </file>
@@ -1503,7 +1693,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1526,12 +1716,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1544,9 +1745,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1563,6 +1761,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1845,23 +2049,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F96"/>
+  <dimension ref="A1:F112"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="73" customWidth="1"/>
-    <col min="3" max="3" width="66.08203125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="90.33203125" style="9" customWidth="1"/>
     <col min="4" max="4" width="10.83203125" customWidth="1"/>
     <col min="5" max="5" width="11.5" customWidth="1"/>
     <col min="6" max="6" width="49.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="8"/>
+      <c r="A1" s="7"/>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -1875,13 +2079,13 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="C2" s="9" t="s">
+      <c r="A2" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -1895,14 +2099,14 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>383</v>
+      <c r="A3" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>381</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>6</v>
@@ -1911,18 +2115,18 @@
         <v>2024</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>382</v>
+      <c r="A4" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>380</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>6</v>
@@ -1935,13 +2139,13 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="C5" s="9" t="s">
+      <c r="A5" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
@@ -1955,13 +2159,13 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="C6" s="9" t="s">
+      <c r="A6" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="2" t="s">
@@ -1975,14 +2179,14 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>193</v>
+      <c r="A7" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>191</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>6</v>
@@ -1995,13 +2199,13 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="C8" s="9" t="s">
+      <c r="A8" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>14</v>
       </c>
       <c r="D8" s="2" t="s">
@@ -2015,13 +2219,13 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="C9" s="9" t="s">
+      <c r="A9" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>16</v>
       </c>
       <c r="D9" s="2" t="s">
@@ -2035,13 +2239,13 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="C10" s="9" t="s">
+      <c r="A10" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D10" s="2" t="s">
@@ -2055,13 +2259,13 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="C11" s="9" t="s">
+      <c r="A11" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>21</v>
       </c>
       <c r="D11" s="2" t="s">
@@ -2075,13 +2279,13 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="C12" s="9" t="s">
+      <c r="A12" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>23</v>
       </c>
       <c r="D12" s="2" t="s">
@@ -2095,13 +2299,13 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="C13" s="9" t="s">
+      <c r="A13" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D13" s="2" t="s">
@@ -2115,13 +2319,13 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="C14" s="9" t="s">
+      <c r="A14" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>29</v>
       </c>
       <c r="D14" s="2" t="s">
@@ -2135,13 +2339,13 @@
       </c>
     </row>
     <row r="15" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="C15" s="9" t="s">
+      <c r="A15" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>31</v>
       </c>
       <c r="D15" s="2" t="s">
@@ -2155,13 +2359,13 @@
       </c>
     </row>
     <row r="16" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="C16" s="9" t="s">
+      <c r="A16" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>33</v>
       </c>
       <c r="D16" s="2" t="s">
@@ -2175,13 +2379,13 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="C17" s="9" t="s">
+      <c r="A17" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>35</v>
       </c>
       <c r="D17" s="2" t="s">
@@ -2195,13 +2399,13 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="C18" s="9" t="s">
+      <c r="A18" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>37</v>
       </c>
       <c r="D18" s="2" t="s">
@@ -2215,13 +2419,13 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="C19" s="9" t="s">
+      <c r="A19" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>39</v>
       </c>
       <c r="D19" s="2" t="s">
@@ -2235,13 +2439,13 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="C20" s="9" t="s">
+      <c r="A20" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>41</v>
       </c>
       <c r="D20" s="2" t="s">
@@ -2255,13 +2459,13 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="C21" s="9" t="s">
+      <c r="A21" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>43</v>
       </c>
       <c r="D21" s="2" t="s">
@@ -2275,13 +2479,13 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="C22" s="9" t="s">
+      <c r="A22" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>45</v>
       </c>
       <c r="D22" s="2" t="s">
@@ -2295,14 +2499,14 @@
       </c>
     </row>
     <row r="23" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>384</v>
+      <c r="A23" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>382</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>6</v>
@@ -2315,13 +2519,13 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="C24" s="9" t="s">
+      <c r="A24" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="C24" s="8" t="s">
         <v>48</v>
       </c>
       <c r="D24" s="2" t="s">
@@ -2335,13 +2539,13 @@
       </c>
     </row>
     <row r="25" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="C25" s="9" t="s">
+      <c r="A25" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="C25" s="8" t="s">
         <v>50</v>
       </c>
       <c r="D25" s="2" t="s">
@@ -2355,13 +2559,13 @@
       </c>
     </row>
     <row r="26" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="C26" s="9" t="s">
+      <c r="A26" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="C26" s="8" t="s">
         <v>52</v>
       </c>
       <c r="D26" s="2" t="s">
@@ -2375,13 +2579,13 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="C27" s="9" t="s">
+      <c r="A27" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="C27" s="8" t="s">
         <v>54</v>
       </c>
       <c r="D27" s="2" t="s">
@@ -2395,13 +2599,13 @@
       </c>
     </row>
     <row r="28" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="C28" s="9" t="s">
+      <c r="A28" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="C28" s="8" t="s">
         <v>56</v>
       </c>
       <c r="D28" s="2" t="s">
@@ -2415,13 +2619,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="C29" s="9" t="s">
+      <c r="A29" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="C29" s="8" t="s">
         <v>59</v>
       </c>
       <c r="D29" s="2" t="s">
@@ -2435,13 +2639,13 @@
       </c>
     </row>
     <row r="30" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="C30" s="9" t="s">
+      <c r="A30" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="C30" s="8" t="s">
         <v>61</v>
       </c>
       <c r="D30" s="2" t="s">
@@ -2455,13 +2659,13 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="C31" s="9" t="s">
+      <c r="A31" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="C31" s="8" t="s">
         <v>63</v>
       </c>
       <c r="D31" s="2" t="s">
@@ -2475,13 +2679,13 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="C32" s="9" t="s">
+      <c r="A32" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="C32" s="8" t="s">
         <v>65</v>
       </c>
       <c r="D32" s="2" t="s">
@@ -2495,13 +2699,13 @@
       </c>
     </row>
     <row r="33" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>320</v>
-      </c>
-      <c r="C33" s="9" t="s">
+      <c r="A33" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="C33" s="8" t="s">
         <v>67</v>
       </c>
       <c r="D33" s="2" t="s">
@@ -2515,13 +2719,13 @@
       </c>
     </row>
     <row r="34" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="C34" s="9" t="s">
+      <c r="A34" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="C34" s="8" t="s">
         <v>69</v>
       </c>
       <c r="D34" s="2" t="s">
@@ -2535,13 +2739,13 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="C35" s="9" t="s">
+      <c r="A35" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="C35" s="8" t="s">
         <v>71</v>
       </c>
       <c r="D35" s="2" t="s">
@@ -2555,13 +2759,13 @@
       </c>
     </row>
     <row r="36" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="C36" s="9" t="s">
+      <c r="A36" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="C36" s="8" t="s">
         <v>73</v>
       </c>
       <c r="D36" s="2" t="s">
@@ -2575,13 +2779,13 @@
       </c>
     </row>
     <row r="37" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="C37" s="9" t="s">
+      <c r="A37" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="C37" s="8" t="s">
         <v>76</v>
       </c>
       <c r="D37" s="2" t="s">
@@ -2595,13 +2799,13 @@
       </c>
     </row>
     <row r="38" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="C38" s="9" t="s">
+      <c r="A38" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="C38" s="8" t="s">
         <v>78</v>
       </c>
       <c r="D38" s="2" t="s">
@@ -2615,13 +2819,13 @@
       </c>
     </row>
     <row r="39" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="C39" s="9" t="s">
+      <c r="A39" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="C39" s="8" t="s">
         <v>80</v>
       </c>
       <c r="D39" s="2" t="s">
@@ -2635,13 +2839,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="C40" s="9" t="s">
+      <c r="A40" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="C40" s="8" t="s">
         <v>82</v>
       </c>
       <c r="D40" s="2" t="s">
@@ -2655,13 +2859,13 @@
       </c>
     </row>
     <row r="41" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="C41" s="9" t="s">
+      <c r="A41" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="C41" s="8" t="s">
         <v>84</v>
       </c>
       <c r="D41" s="2" t="s">
@@ -2675,13 +2879,13 @@
       </c>
     </row>
     <row r="42" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="C42" s="9" t="s">
+      <c r="A42" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="C42" s="8" t="s">
         <v>86</v>
       </c>
       <c r="D42" s="2" t="s">
@@ -2695,14 +2899,14 @@
       </c>
     </row>
     <row r="43" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>385</v>
+      <c r="A43" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>383</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>6</v>
@@ -2715,13 +2919,13 @@
       </c>
     </row>
     <row r="44" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="C44" s="9" t="s">
+      <c r="A44" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="C44" s="8" t="s">
         <v>89</v>
       </c>
       <c r="D44" s="2" t="s">
@@ -2735,13 +2939,13 @@
       </c>
     </row>
     <row r="45" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="C45" s="9" t="s">
+      <c r="A45" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="C45" s="8" t="s">
         <v>91</v>
       </c>
       <c r="D45" s="2" t="s">
@@ -2750,18 +2954,18 @@
       <c r="E45" s="3">
         <v>2024</v>
       </c>
-      <c r="F45" s="6" t="s">
+      <c r="F45" s="5" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="C46" s="9" t="s">
+      <c r="A46" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="C46" s="8" t="s">
         <v>93</v>
       </c>
       <c r="D46" s="2" t="s">
@@ -2770,18 +2974,18 @@
       <c r="E46" s="3">
         <v>2024</v>
       </c>
-      <c r="F46" s="6" t="s">
+      <c r="F46" s="5" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="C47" s="9" t="s">
+      <c r="A47" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="C47" s="8" t="s">
         <v>95</v>
       </c>
       <c r="D47" s="2" t="s">
@@ -2790,18 +2994,18 @@
       <c r="E47" s="3">
         <v>2024</v>
       </c>
-      <c r="F47" s="6" t="s">
+      <c r="F47" s="5" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="B48" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="C48" s="9" t="s">
+      <c r="A48" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="C48" s="8" t="s">
         <v>98</v>
       </c>
       <c r="D48" s="2" t="s">
@@ -2810,219 +3014,219 @@
       <c r="E48" s="3">
         <v>2024</v>
       </c>
-      <c r="F48" s="7" t="s">
+      <c r="F48" s="6" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E49" s="3">
+        <v>2024</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E50" s="3">
+        <v>2024</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="B49" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="C49" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E49" s="3">
-        <v>2024</v>
-      </c>
-      <c r="F49" s="6" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="8" t="s">
+      <c r="B51" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E51" s="3">
+        <v>2024</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="B52" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="C50" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E50" s="3">
-        <v>2024</v>
-      </c>
-      <c r="F50" s="6" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="8" t="s">
+      <c r="C52" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E52" s="3">
+        <v>2024</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="B53" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="C51" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E51" s="3">
-        <v>2024</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="8" t="s">
+      <c r="C53" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E53" s="3">
+        <v>2024</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="B52" s="8" t="s">
+      <c r="B54" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="C52" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E52" s="3">
-        <v>2024</v>
-      </c>
-      <c r="F52" s="6" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="8" t="s">
+      <c r="C54" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E54" s="3">
+        <v>2024</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="B53" s="8" t="s">
+      <c r="B55" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="C53" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E53" s="3">
-        <v>2024</v>
-      </c>
-      <c r="F53" s="6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="8" t="s">
+      <c r="C55" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E55" s="3">
+        <v>2024</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A56" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="B56" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="C54" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E54" s="3">
-        <v>2024</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="8" t="s">
+      <c r="C56" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E56" s="3">
+        <v>2024</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A57" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="B55" s="8" t="s">
+      <c r="B57" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="C55" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E55" s="3">
-        <v>2024</v>
-      </c>
-      <c r="F55" s="6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="8" t="s">
+      <c r="C57" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2024</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A58" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="B56" s="8" t="s">
+      <c r="B58" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="C56" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E56" s="3">
-        <v>2024</v>
-      </c>
-      <c r="F56" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="8" t="s">
+      <c r="C58" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2024</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A59" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="B57" s="8" t="s">
+      <c r="B59" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="C57" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E57" s="3">
-        <v>2024</v>
-      </c>
-      <c r="F57" s="6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="B58" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="C58" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E58" s="3">
-        <v>2024</v>
-      </c>
-      <c r="F58" s="6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="B59" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="C59" s="9" t="s">
-        <v>387</v>
+      <c r="C59" s="8" t="s">
+        <v>385</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>119</v>
@@ -3030,58 +3234,58 @@
       <c r="E59" s="3">
         <v>2024</v>
       </c>
-      <c r="F59" s="6" t="s">
+      <c r="F59" s="5" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2024</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A61" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2024</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B62" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="C60" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E60" s="3">
-        <v>2024</v>
-      </c>
-      <c r="F60" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="B61" s="8" t="s">
-        <v>346</v>
-      </c>
-      <c r="C61" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E61" s="3">
-        <v>2024</v>
-      </c>
-      <c r="F61" s="6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="B62" s="8" t="s">
-        <v>347</v>
-      </c>
-      <c r="C62" s="9" t="s">
+      <c r="C62" s="8" t="s">
         <v>124</v>
       </c>
       <c r="D62" s="2" t="s">
@@ -3095,13 +3299,13 @@
       </c>
     </row>
     <row r="63" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="B63" s="8" t="s">
-        <v>348</v>
-      </c>
-      <c r="C63" s="9" t="s">
+      <c r="A63" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="C63" s="8" t="s">
         <v>126</v>
       </c>
       <c r="D63" s="2" t="s">
@@ -3115,13 +3319,13 @@
       </c>
     </row>
     <row r="64" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="B64" s="8" t="s">
-        <v>349</v>
-      </c>
-      <c r="C64" s="9" t="s">
+      <c r="A64" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="C64" s="8" t="s">
         <v>129</v>
       </c>
       <c r="D64" s="2" t="s">
@@ -3135,13 +3339,13 @@
       </c>
     </row>
     <row r="65" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="8" t="s">
-        <v>258</v>
-      </c>
-      <c r="B65" s="8" t="s">
-        <v>350</v>
-      </c>
-      <c r="C65" s="9" t="s">
+      <c r="A65" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="C65" s="8" t="s">
         <v>131</v>
       </c>
       <c r="D65" s="2" t="s">
@@ -3155,13 +3359,13 @@
       </c>
     </row>
     <row r="66" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="B66" s="8" t="s">
-        <v>351</v>
-      </c>
-      <c r="C66" s="9" t="s">
+      <c r="A66" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="C66" s="8" t="s">
         <v>133</v>
       </c>
       <c r="D66" s="2" t="s">
@@ -3175,13 +3379,13 @@
       </c>
     </row>
     <row r="67" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="B67" s="8" t="s">
-        <v>352</v>
-      </c>
-      <c r="C67" s="9" t="s">
+      <c r="A67" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C67" s="8" t="s">
         <v>135</v>
       </c>
       <c r="D67" s="2" t="s">
@@ -3195,13 +3399,13 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="B68" s="8" t="s">
-        <v>353</v>
-      </c>
-      <c r="C68" s="9" t="s">
+      <c r="A68" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="C68" s="8" t="s">
         <v>138</v>
       </c>
       <c r="D68" s="2" t="s">
@@ -3215,13 +3419,13 @@
       </c>
     </row>
     <row r="69" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="8" t="s">
-        <v>262</v>
-      </c>
-      <c r="B69" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="C69" s="9" t="s">
+      <c r="A69" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="C69" s="8" t="s">
         <v>141</v>
       </c>
       <c r="D69" s="2" t="s">
@@ -3235,13 +3439,13 @@
       </c>
     </row>
     <row r="70" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="B70" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="C70" s="9" t="s">
+      <c r="A70" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="C70" s="8" t="s">
         <v>144</v>
       </c>
       <c r="D70" s="2" t="s">
@@ -3255,13 +3459,13 @@
       </c>
     </row>
     <row r="71" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="B71" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="C71" s="9" t="s">
+      <c r="A71" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="C71" s="8" t="s">
         <v>147</v>
       </c>
       <c r="D71" s="2" t="s">
@@ -3275,14 +3479,14 @@
       </c>
     </row>
     <row r="72" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="B72" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="C72" s="9" t="s">
-        <v>389</v>
+      <c r="A72" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>387</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>6</v>
@@ -3295,13 +3499,13 @@
       </c>
     </row>
     <row r="73" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="B73" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="C73" s="9" t="s">
+      <c r="A73" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="C73" s="8" t="s">
         <v>151</v>
       </c>
       <c r="D73" s="2" t="s">
@@ -3315,13 +3519,13 @@
       </c>
     </row>
     <row r="74" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="8" t="s">
-        <v>267</v>
-      </c>
-      <c r="B74" s="8" t="s">
-        <v>360</v>
-      </c>
-      <c r="C74" s="9" t="s">
+      <c r="A74" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="C74" s="8" t="s">
         <v>153</v>
       </c>
       <c r="D74" s="2" t="s">
@@ -3335,13 +3539,13 @@
       </c>
     </row>
     <row r="75" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="B75" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="C75" s="9" t="s">
+      <c r="A75" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C75" s="8" t="s">
         <v>155</v>
       </c>
       <c r="D75" s="2" t="s">
@@ -3355,13 +3559,13 @@
       </c>
     </row>
     <row r="76" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="8" t="s">
-        <v>269</v>
-      </c>
-      <c r="B76" s="8" t="s">
-        <v>362</v>
-      </c>
-      <c r="C76" s="9" t="s">
+      <c r="A76" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="C76" s="8" t="s">
         <v>157</v>
       </c>
       <c r="D76" s="2" t="s">
@@ -3375,14 +3579,14 @@
       </c>
     </row>
     <row r="77" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="B77" s="8" t="s">
-        <v>363</v>
-      </c>
-      <c r="C77" s="9" t="s">
-        <v>390</v>
+      <c r="A77" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>388</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>92</v>
@@ -3395,13 +3599,13 @@
       </c>
     </row>
     <row r="78" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="B78" s="8" t="s">
-        <v>364</v>
-      </c>
-      <c r="C78" s="9" t="s">
+      <c r="A78" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="C78" s="8" t="s">
         <v>160</v>
       </c>
       <c r="D78" s="2" t="s">
@@ -3415,13 +3619,13 @@
       </c>
     </row>
     <row r="79" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="B79" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="C79" s="9" t="s">
+      <c r="A79" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="C79" s="8" t="s">
         <v>162</v>
       </c>
       <c r="D79" s="2" t="s">
@@ -3435,13 +3639,13 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="B80" s="8" t="s">
-        <v>366</v>
-      </c>
-      <c r="C80" s="9" t="s">
+      <c r="A80" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="C80" s="8" t="s">
         <v>164</v>
       </c>
       <c r="D80" s="2" t="s">
@@ -3455,13 +3659,13 @@
       </c>
     </row>
     <row r="81" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="B81" s="8" t="s">
-        <v>367</v>
-      </c>
-      <c r="C81" s="9" t="s">
+      <c r="A81" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="C81" s="8" t="s">
         <v>166</v>
       </c>
       <c r="D81" s="2" t="s">
@@ -3475,14 +3679,14 @@
       </c>
     </row>
     <row r="82" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="B82" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="C82" s="9" t="s">
-        <v>391</v>
+      <c r="A82" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>389</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>6</v>
@@ -3495,13 +3699,13 @@
       </c>
     </row>
     <row r="83" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A83" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="B83" s="8" t="s">
-        <v>369</v>
-      </c>
-      <c r="C83" s="9" t="s">
+      <c r="A83" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="C83" s="8" t="s">
         <v>169</v>
       </c>
       <c r="D83" s="2" t="s">
@@ -3515,14 +3719,14 @@
       </c>
     </row>
     <row r="84" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A84" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="B84" s="8" t="s">
-        <v>370</v>
-      </c>
-      <c r="C84" s="9" t="s">
-        <v>392</v>
+      <c r="A84" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>390</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>139</v>
@@ -3530,18 +3734,18 @@
       <c r="E84" s="3">
         <v>2023</v>
       </c>
-      <c r="F84" s="5" t="s">
+      <c r="F84" s="4" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A85" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="B85" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="C85" s="9" t="s">
+      <c r="A85" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="C85" s="8" t="s">
         <v>172</v>
       </c>
       <c r="D85" s="2" t="s">
@@ -3555,13 +3759,13 @@
       </c>
     </row>
     <row r="86" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A86" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="B86" s="8" t="s">
-        <v>372</v>
-      </c>
-      <c r="C86" s="9" t="s">
+      <c r="A86" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C86" s="8" t="s">
         <v>174</v>
       </c>
       <c r="D86" s="2" t="s">
@@ -3575,13 +3779,13 @@
       </c>
     </row>
     <row r="87" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A87" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="B87" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="C87" s="9" t="s">
+      <c r="A87" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="C87" s="8" t="s">
         <v>176</v>
       </c>
       <c r="D87" s="2" t="s">
@@ -3595,13 +3799,13 @@
       </c>
     </row>
     <row r="88" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A88" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="B88" s="8" t="s">
-        <v>374</v>
-      </c>
-      <c r="C88" s="9" t="s">
+      <c r="A88" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="C88" s="8" t="s">
         <v>178</v>
       </c>
       <c r="D88" s="2" t="s">
@@ -3615,13 +3819,13 @@
       </c>
     </row>
     <row r="89" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A89" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="B89" s="8" t="s">
-        <v>375</v>
-      </c>
-      <c r="C89" s="9" t="s">
+      <c r="A89" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="C89" s="8" t="s">
         <v>180</v>
       </c>
       <c r="D89" s="2" t="s">
@@ -3635,13 +3839,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A90" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="B90" s="8" t="s">
-        <v>376</v>
-      </c>
-      <c r="C90" s="9" t="s">
+      <c r="A90" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="C90" s="8" t="s">
         <v>182</v>
       </c>
       <c r="D90" s="2" t="s">
@@ -3650,19 +3854,19 @@
       <c r="E90" s="3">
         <v>2023</v>
       </c>
-      <c r="F90" s="4" t="s">
+      <c r="F90" s="12" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A91" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="C91" s="8" t="s">
         <v>183</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A91" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="B91" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="C91" s="9" t="s">
-        <v>184</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>127</v>
@@ -3671,18 +3875,18 @@
         <v>2023</v>
       </c>
       <c r="F91" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A92" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="C92" s="8" t="s">
         <v>185</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A92" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="B92" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="C92" s="9" t="s">
-        <v>186</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>6</v>
@@ -3691,18 +3895,18 @@
         <v>2023</v>
       </c>
       <c r="F92" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A93" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="C93" s="8" t="s">
         <v>187</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A93" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="B93" s="8" t="s">
-        <v>379</v>
-      </c>
-      <c r="C93" s="9" t="s">
-        <v>188</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>127</v>
@@ -3710,19 +3914,19 @@
       <c r="E93" s="3">
         <v>2023</v>
       </c>
-      <c r="F93" s="6" t="s">
+      <c r="F93" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A94" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="C94" s="8" t="s">
         <v>189</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A94" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="B94" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="C94" s="9" t="s">
-        <v>190</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>27</v>
@@ -3730,19 +3934,19 @@
       <c r="E94" s="3">
         <v>2023</v>
       </c>
-      <c r="F94" s="6" t="s">
+      <c r="F94" s="4" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A95" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="B95" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="C95" s="9" t="s">
-        <v>194</v>
+      <c r="A95" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>192</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>6</v>
@@ -3751,11 +3955,274 @@
         <v>2022</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="8"/>
+        <v>428</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A96" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E96" s="3">
+        <v>2024</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A97" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="B97" t="s">
+        <v>426</v>
+      </c>
+      <c r="C97" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E97" s="11">
+        <v>2024</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A98" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="C98" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E98" s="3">
+        <v>2024</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A99" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E99" s="3">
+        <v>2024</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A100" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="E100" s="3">
+        <v>2025</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A101" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>414</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E101" s="3">
+        <v>2023</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A102" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="C102" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="E102" s="3">
+        <v>2025</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A103" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="C103" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="E103" s="3">
+        <v>2024</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A104" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="E104" s="3">
+        <v>2023</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A105" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="B105" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="C105" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="E105" s="3">
+        <v>2024</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A106" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="E106" s="3">
+        <v>2024</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A107" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="B107" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="E107" s="3">
+        <v>2025</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C108" s="8"/>
+      <c r="D108" s="2"/>
+      <c r="E108" s="3"/>
+      <c r="F108" s="4"/>
+    </row>
+    <row r="109" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C109" s="8"/>
+      <c r="D109" s="2"/>
+      <c r="E109" s="3"/>
+      <c r="F109" s="4"/>
+    </row>
+    <row r="110" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C110" s="8"/>
+      <c r="D110" s="2"/>
+      <c r="E110" s="3"/>
+      <c r="F110" s="4"/>
+    </row>
+    <row r="111" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E111" s="3"/>
+      <c r="F111" s="4"/>
+    </row>
+    <row r="112" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="E112" s="3"/>
+      <c r="F112" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3780,8 +4247,14 @@
     <hyperlink ref="F93" r:id="rId18" xr:uid="{7F4D5E21-1332-483F-A474-1C5AC0109E4B}"/>
     <hyperlink ref="F94" r:id="rId19" xr:uid="{17E531BA-A754-46D9-A690-EE9AE12DCDEC}"/>
     <hyperlink ref="F3" r:id="rId20" xr:uid="{F14756AD-6991-45DD-9B60-29A611CF0F49}"/>
+    <hyperlink ref="F98" r:id="rId21" xr:uid="{656BDAFC-C50F-4A50-BBDB-94893D536E0F}"/>
+    <hyperlink ref="F99" r:id="rId22" xr:uid="{58E5533B-D819-40EF-B07D-09DCE8FA7D41}"/>
+    <hyperlink ref="F95" r:id="rId23" xr:uid="{BEA41AA3-120E-4A03-A5C2-FE4F8A4C1561}"/>
+    <hyperlink ref="F97" r:id="rId24" xr:uid="{D048FC92-D31A-43BF-953B-8548FF711049}"/>
+    <hyperlink ref="F90" r:id="rId25" xr:uid="{BD91D05C-2EE2-417C-9AED-E1DFC06C5786}"/>
+    <hyperlink ref="F96" r:id="rId26" xr:uid="{F222FDA5-760B-4628-86B5-93929C1C959E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId21"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId27"/>
 </worksheet>
 </file>